--- a/artfynd/S 3571-2021 artfynd.xlsx
+++ b/artfynd/S 3571-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Linköpings kommuns hotartsdatabas 2012</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111178</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16855545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16855546</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
           <t>Linköpings kommuns hotartsdatabas 2012</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130898</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
           <t>Linköpings kommuns hotartsdatabas 2012</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/284088</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Linköpings kommuns hotartsdatabas 2012</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/368677</t>
         </is>
       </c>
     </row>
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16855547</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737067</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737074</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16855550</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737066</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16855549</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737072</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2217,6 +2287,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90972731</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2333,6 +2408,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737068</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2449,6 +2529,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737069</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2565,6 +2650,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737070</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2683,6 +2773,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57504539</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2801,8 +2896,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57504541</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>